--- a/results/technical_validation/df_comparison_metallican_nrcan.xlsx
+++ b/results/technical_validation/df_comparison_metallican_nrcan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca0-my.sharepoint.com/personal/marin_pellan_polymtlus_ca/Documents/Desktop/POST_DOC/Project/canada_metal_sustainability_db/results/technical_validation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/metallican_db/results/technical_validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_34458EB1D26A840E62355476585DCE3A874749FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{791B9959-6F2F-4CD0-B9BA-018CE2648458}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="11_34458EB1D26A840E62355476585DCE3A874749FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2AA851-CC5E-4F1D-9FA1-9F1B6C93DD9C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -789,19 +789,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J134"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -818,7 +818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -835,7 +835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -851,8 +851,9 @@
       <c r="E3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -869,7 +870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -886,7 +887,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -904,7 +905,7 @@
       </c>
       <c r="G6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -921,7 +922,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -938,7 +939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>21</v>
       </c>
@@ -955,7 +956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -972,7 +973,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -989,7 +990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1024,7 +1025,7 @@
       </c>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
@@ -1042,7 +1043,7 @@
       </c>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1059,7 +1060,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -1077,7 +1078,7 @@
       </c>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -1094,7 +1095,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -1111,7 +1112,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -1145,7 +1146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>30</v>
       </c>
@@ -1162,7 +1163,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>30</v>
       </c>
@@ -1179,7 +1180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1193,7 +1194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -1210,7 +1211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -1244,7 +1245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -1261,7 +1262,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>38</v>
       </c>
@@ -1278,7 +1279,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -1295,7 +1296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>51</v>
       </c>
@@ -1329,7 +1330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>53</v>
       </c>
@@ -1346,7 +1347,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>53</v>
       </c>
@@ -1363,7 +1364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>53</v>
       </c>
@@ -1380,7 +1381,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>53</v>
       </c>
@@ -1397,7 +1398,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>53</v>
       </c>
@@ -1415,7 +1416,7 @@
       </c>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>53</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>53</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>53</v>
       </c>
@@ -1483,7 +1484,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>53</v>
       </c>
@@ -1500,7 +1501,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>53</v>
       </c>
@@ -1517,7 +1518,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>53</v>
       </c>
@@ -1534,7 +1535,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>53</v>
       </c>
@@ -1551,7 +1552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>53</v>
       </c>
@@ -1568,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>53</v>
       </c>
@@ -1585,7 +1586,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>53</v>
       </c>
@@ -1602,7 +1603,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>53</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>53</v>
       </c>
@@ -1636,7 +1637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>64</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -1670,7 +1671,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>68</v>
       </c>
@@ -1687,7 +1688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>70</v>
       </c>
@@ -1721,7 +1722,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>70</v>
       </c>
@@ -1738,7 +1739,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>70</v>
       </c>
@@ -1755,7 +1756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>70</v>
       </c>
@@ -1772,7 +1773,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>70</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>70</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>70</v>
       </c>
@@ -1823,7 +1824,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>70</v>
       </c>
@@ -1840,7 +1841,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -1857,7 +1858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -1874,7 +1875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>77</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>80</v>
       </c>
@@ -1925,7 +1926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>80</v>
       </c>
@@ -1942,7 +1943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -1959,7 +1960,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -1993,7 +1994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>83</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -2044,7 +2045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>85</v>
       </c>
@@ -2061,7 +2062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2095,7 +2096,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -2112,7 +2113,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>87</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>87</v>
       </c>
@@ -2146,7 +2147,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>87</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>87</v>
       </c>
@@ -2180,7 +2181,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>87</v>
       </c>
@@ -2197,7 +2198,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>87</v>
       </c>
@@ -2214,7 +2215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>87</v>
       </c>
@@ -2231,7 +2232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>89</v>
       </c>
@@ -2248,7 +2249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>90</v>
       </c>
@@ -2265,7 +2266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>92</v>
       </c>
@@ -2282,7 +2283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>92</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -2316,7 +2317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>92</v>
       </c>
@@ -2350,7 +2351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -2367,7 +2368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -2384,7 +2385,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -2401,7 +2402,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>96</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>97</v>
       </c>
@@ -2435,7 +2436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2469,7 +2470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2486,7 +2487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -2503,7 +2504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -2520,7 +2521,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>99</v>
       </c>
@@ -2537,7 +2538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2554,7 +2555,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2571,7 +2572,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2588,7 +2589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2622,7 +2623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>109</v>
       </c>
@@ -2639,7 +2640,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>109</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>109</v>
       </c>
@@ -2673,7 +2674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>109</v>
       </c>
@@ -2690,7 +2691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>109</v>
       </c>
@@ -2707,7 +2708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>109</v>
       </c>
@@ -2724,7 +2725,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>109</v>
       </c>
@@ -2741,7 +2742,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>109</v>
       </c>
@@ -2758,7 +2759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>109</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>109</v>
       </c>
@@ -2792,7 +2793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>111</v>
       </c>
@@ -2809,7 +2810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>111</v>
       </c>
@@ -2826,7 +2827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>111</v>
       </c>
@@ -2843,7 +2844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>115</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>117</v>
       </c>
@@ -2877,7 +2878,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>118</v>
       </c>
@@ -2894,7 +2895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="124" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -2911,7 +2912,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="125" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>121</v>
       </c>
@@ -2962,7 +2963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>122</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>123</v>
       </c>
@@ -2993,7 +2994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>123</v>
       </c>
@@ -3010,7 +3011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>123</v>
       </c>
@@ -3027,7 +3028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>123</v>
       </c>
@@ -3044,7 +3045,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>123</v>
       </c>
@@ -3061,7 +3062,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>123</v>
       </c>
